--- a/frontend/test-fixtures/case4_invalid_role.xlsx
+++ b/frontend/test-fixtures/case4_invalid_role.xlsx
@@ -29,7 +29,7 @@
     <t>Nhân sự Role Lạ</t>
   </si>
   <si>
-    <t>role_invalid_1791232548812@company.local</t>
+    <t>role_invalid_1791313638710@company.local</t>
   </si>
   <si>
     <t>Kỹ thuật</t>

--- a/frontend/test-fixtures/case4_invalid_role.xlsx
+++ b/frontend/test-fixtures/case4_invalid_role.xlsx
@@ -29,7 +29,7 @@
     <t>Nhân sự Role Lạ</t>
   </si>
   <si>
-    <t>role_invalid_1791313638710@company.local</t>
+    <t>role_invalid_1791364218252@company.local</t>
   </si>
   <si>
     <t>Kỹ thuật</t>

--- a/frontend/test-fixtures/case4_invalid_role.xlsx
+++ b/frontend/test-fixtures/case4_invalid_role.xlsx
@@ -29,7 +29,7 @@
     <t>Nhân sự Role Lạ</t>
   </si>
   <si>
-    <t>role_invalid_1791364218252@company.local</t>
+    <t>role_invalid_1791476314118@company.local</t>
   </si>
   <si>
     <t>Kỹ thuật</t>

--- a/frontend/test-fixtures/case4_invalid_role.xlsx
+++ b/frontend/test-fixtures/case4_invalid_role.xlsx
@@ -29,7 +29,7 @@
     <t>Nhân sự Role Lạ</t>
   </si>
   <si>
-    <t>role_invalid_1791476314118@company.local</t>
+    <t>role_invalid_1791567428307@company.local</t>
   </si>
   <si>
     <t>Kỹ thuật</t>

--- a/frontend/test-fixtures/case4_invalid_role.xlsx
+++ b/frontend/test-fixtures/case4_invalid_role.xlsx
@@ -29,7 +29,7 @@
     <t>Nhân sự Role Lạ</t>
   </si>
   <si>
-    <t>role_invalid_1791567428307@company.local</t>
+    <t>role_invalid_1791567643572@company.local</t>
   </si>
   <si>
     <t>Kỹ thuật</t>

--- a/frontend/test-fixtures/case4_invalid_role.xlsx
+++ b/frontend/test-fixtures/case4_invalid_role.xlsx
@@ -29,7 +29,7 @@
     <t>Nhân sự Role Lạ</t>
   </si>
   <si>
-    <t>role_invalid_1791567643572@company.local</t>
+    <t>role_invalid_1791909724777@company.local</t>
   </si>
   <si>
     <t>Kỹ thuật</t>

--- a/frontend/test-fixtures/case4_invalid_role.xlsx
+++ b/frontend/test-fixtures/case4_invalid_role.xlsx
@@ -29,7 +29,7 @@
     <t>Nhân sự Role Lạ</t>
   </si>
   <si>
-    <t>role_invalid_1791567643572@company.local</t>
+    <t>role_invalid_1792700857270@company.local</t>
   </si>
   <si>
     <t>Kỹ thuật</t>
